--- a/docker_refactor/docs/LabPulse Sensors.xlsx
+++ b/docker_refactor/docs/LabPulse Sensors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LabPulse Tommy\LabPulse\docker_refactor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E2FDF5A-51EA-4C3E-BA49-E659639F97FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDECCE7B-8D60-4D83-92E9-3E72C4E1EFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{BEA7CCE9-7876-423F-8F4B-DF57CA569CE3}"/>
   </bookViews>
@@ -113,9 +113,6 @@
     <t>Triton 1/2 (Unknown Model)</t>
   </si>
   <si>
-    <t>UPS Hat</t>
-  </si>
-  <si>
     <t>Power</t>
   </si>
   <si>
@@ -129,6 +126,9 @@
   </si>
   <si>
     <t>Present - 0 Reading</t>
+  </si>
+  <si>
+    <t>UPS Hat (ITS NOT THIS)</t>
   </si>
 </sst>
 </file>
@@ -562,7 +562,7 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -582,7 +582,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -602,7 +602,7 @@
         <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -622,7 +622,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -642,7 +642,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -662,7 +662,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -708,27 +708,27 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J9" t="s">
         <v>5</v>
@@ -754,7 +754,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J10" t="s">
         <v>8</v>
@@ -773,7 +773,7 @@
     <hyperlink ref="A3" r:id="rId3" xr:uid="{C513B426-BB3D-4ABF-89F3-FB01FBBF1EF7}"/>
     <hyperlink ref="A4" r:id="rId4" xr:uid="{CAC0849B-33AA-402F-98D2-BFBB8AF0417E}"/>
     <hyperlink ref="A10" r:id="rId5" xr:uid="{06AD4B34-F348-42CD-9811-25DD6FE397E7}"/>
-    <hyperlink ref="A9" r:id="rId6" xr:uid="{55BB8C77-91EB-49B6-BB4A-9A01D369BDE7}"/>
+    <hyperlink ref="A9" r:id="rId6" display="UPS Hat" xr:uid="{55BB8C77-91EB-49B6-BB4A-9A01D369BDE7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
